--- a/packages/calculators/src/modules/test/4.1-feedlot-manure/4.1-feedlot-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.1-feedlot-manure/4.1-feedlot-manure.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.1-feedlot-manure/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE8545E-BAFB-8244-AEBA-A129830E79A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48D68E0-2752-CE40-80EB-D363D7524CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-3600" windowWidth="38400" windowHeight="21600" activeTab="7" xr2:uid="{41363ED7-B38E-4D41-B794-96D6D87F84EC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="7" xr2:uid="{41363ED7-B38E-4D41-B794-96D6D87F84EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Input Scenarios" sheetId="1" r:id="rId1"/>
@@ -22,7 +17,10 @@
     <sheet name="4.1.1.5" sheetId="7" r:id="rId7"/>
     <sheet name="4.1.1.6" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -508,8 +506,8 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -526,6 +524,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2042,8 +2065,8 @@
         <v>93</v>
       </c>
       <c r="B33">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="E33" s="11">
         <v>27</v>
@@ -3247,11 +3270,11 @@
         <v>8.5578694655999985E-4</v>
       </c>
       <c r="Y9">
-        <f>(1-$T9)*$O9*$P9*$Q9*G9*V9</f>
+        <f t="shared" ref="Y9:Z12" si="3">(1-$T9)*$O9*$P9*$Q9*G9*V9</f>
         <v>6.4184020991999986E-4</v>
       </c>
       <c r="Z9">
-        <f>(1-$T9)*$O9*$P9*$Q9*H9*W9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA9">
@@ -3263,15 +3286,15 @@
         <v>0.8</v>
       </c>
       <c r="AC9">
-        <f t="shared" ref="AC9:AC12" si="3">O9*AA9*AB9*P9*Q9</f>
+        <f t="shared" ref="AC9:AC12" si="4">O9*AA9*AB9*P9*Q9</f>
         <v>3.4231477862399994E-3</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD9:AD12" si="4">S9+SUM(X9:Z9)+AC9</f>
+        <f t="shared" ref="AD9:AD12" si="5">S9+SUM(X9:Z9)+AC9</f>
         <v>1.1339177041919998E-2</v>
       </c>
       <c r="AE9">
-        <f t="shared" ref="AE9:AE12" si="5">D9*E9*AD9/1000</f>
+        <f t="shared" ref="AE9:AE12" si="6">D9*E9*AD9/1000</f>
         <v>0.18142683267071996</v>
       </c>
     </row>
@@ -3373,11 +3396,11 @@
         <v>8.8870182911999997E-4</v>
       </c>
       <c r="Y10">
-        <f>(1-$T10)*$O10*$P10*$Q10*G10*V10</f>
+        <f t="shared" si="3"/>
         <v>4.4435091455999998E-4</v>
       </c>
       <c r="Z10">
-        <f>(1-$T10)*$O10*$P10*$Q10*H10*W10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA10">
@@ -3389,15 +3412,15 @@
         <v>0.78</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.4659371335679996E-3</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.0207444500479995E-3</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11373606009077759</v>
       </c>
     </row>
@@ -3499,11 +3522,11 @@
         <v>8.8870182911999997E-4</v>
       </c>
       <c r="Y11">
-        <f>(1-$T11)*$O11*$P11*$Q11*G11*V11</f>
+        <f t="shared" si="3"/>
         <v>4.4435091455999998E-4</v>
       </c>
       <c r="Z11">
-        <f>(1-$T11)*$O11*$P11*$Q11*H11*W11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA11">
@@ -3515,15 +3538,15 @@
         <v>0.75</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.3326318591999993E-3</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.8874391756799987E-3</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.27549756702719996</v>
       </c>
     </row>
@@ -3625,11 +3648,11 @@
         <v>6.7475509247999987E-4</v>
       </c>
       <c r="Y12">
-        <f>(1-$T12)*$O12*$P12*$Q12*G12*V12</f>
+        <f t="shared" si="3"/>
         <v>5.0606631935999982E-4</v>
       </c>
       <c r="Z12">
-        <f>(1-$T12)*$O12*$P12*$Q12*H12*W12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA12">
@@ -3641,15 +3664,15 @@
         <v>0.8</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6990203699199995E-3</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.5667295129599986E-3</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.22378252642099192</v>
       </c>
     </row>
@@ -3912,15 +3935,15 @@
         <v>2929.8913280000006</v>
       </c>
       <c r="V8">
-        <f>$T8*F8</f>
+        <f t="shared" ref="V8:X12" si="0">$T8*F8</f>
         <v>439.01491658752013</v>
       </c>
       <c r="W8">
-        <f>$T8*G8</f>
+        <f t="shared" si="0"/>
         <v>439.01491658752013</v>
       </c>
       <c r="X8">
-        <f>$T8*H8</f>
+        <f t="shared" si="0"/>
         <v>219.50745829376007</v>
       </c>
       <c r="Y8">
@@ -3949,31 +3972,31 @@
       </c>
       <c r="AE8">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF8">
         <f>U8*Z8*$AE8</f>
-        <v>24.862220697600009</v>
+        <v>24.83961867878401</v>
       </c>
       <c r="AG8">
-        <f t="shared" ref="AG8:AJ8" si="0">V8*AA8*$AE8</f>
-        <v>3.4494029160448014</v>
+        <f t="shared" ref="AG8:AJ8" si="1">V8*AA8*$AE8</f>
+        <v>3.4462670952120336</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="0"/>
-        <v>6.8988058320896029</v>
+        <f t="shared" si="1"/>
+        <v>6.8925341904240671</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK8">
         <f>SUM(AF8:AJ8)/1000</f>
-        <v>3.5210429445734409E-2</v>
+        <v>3.5178419964420109E-2</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.2">
@@ -4034,15 +4057,15 @@
         <v>6.25</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O12" si="1">J9*M9/N9</f>
+        <f t="shared" ref="O9:O12" si="2">J9*M9/N9</f>
         <v>0.23296000000000003</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:P12" si="2">O9*(1-K9)</f>
+        <f t="shared" ref="P9:P12" si="3">O9*(1-K9)</f>
         <v>0.18543616000000004</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q9:Q12" si="3">D9*E9*P9</f>
+        <f t="shared" ref="Q9:Q12" si="4">D9*E9*P9</f>
         <v>2966.9785600000009</v>
       </c>
       <c r="R9">
@@ -4062,19 +4085,19 @@
         <v>2966.9785600000009</v>
       </c>
       <c r="V9">
-        <f>$T9*F9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="W9">
-        <f>$T9*G9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="X9">
-        <f>$T9*H9</f>
+        <f t="shared" si="0"/>
         <v>222.28603371520003</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="4">Q9*R9</f>
+        <f t="shared" ref="Y9:Y12" si="5">Q9*R9</f>
         <v>59.339571200000023</v>
       </c>
       <c r="Z9">
@@ -4099,31 +4122,31 @@
       </c>
       <c r="AE9">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF9">
-        <f t="shared" ref="AF9:AF12" si="5">U9*Z9*$AE9</f>
-        <v>25.176932352000009</v>
+        <f t="shared" ref="AF9:AF12" si="6">U9*Z9*$AE9</f>
+        <v>25.154044231680007</v>
       </c>
       <c r="AG9">
-        <f t="shared" ref="AG9:AG12" si="6">V9*AA9*$AE9</f>
-        <v>3.4930662440960005</v>
+        <f t="shared" ref="AG9:AG12" si="7">V9*AA9*$AE9</f>
+        <v>3.4898907293286405</v>
       </c>
       <c r="AH9">
-        <f t="shared" ref="AH9:AH12" si="7">W9*AB9*$AE9</f>
-        <v>6.9861324881920011</v>
+        <f t="shared" ref="AH9:AH12" si="8">W9*AB9*$AE9</f>
+        <v>6.9797814586572811</v>
       </c>
       <c r="AI9">
-        <f t="shared" ref="AI9:AI12" si="8">X9*AC9*$AE9</f>
+        <f t="shared" ref="AI9:AI12" si="9">X9*AC9*$AE9</f>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" ref="AJ9:AJ12" si="9">Y9*AD9*$AE9</f>
+        <f t="shared" ref="AJ9:AJ12" si="10">Y9*AD9*$AE9</f>
         <v>0</v>
       </c>
       <c r="AK9">
-        <f t="shared" ref="AK9:AK12" si="10">SUM(AF9:AJ9)/1000</f>
-        <v>3.5656131084288008E-2</v>
+        <f t="shared" ref="AK9:AK12" si="11">SUM(AF9:AJ9)/1000</f>
+        <v>3.5623716419665927E-2</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.2">
@@ -4184,15 +4207,15 @@
         <v>6.25</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2932.6095360000004</v>
       </c>
       <c r="R10">
@@ -4212,19 +4235,19 @@
         <v>2932.6095360000004</v>
       </c>
       <c r="V10">
-        <f>$T10*F10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="W10">
-        <f>$T10*G10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="X10">
-        <f>$T10*H10</f>
+        <f t="shared" si="0"/>
         <v>219.71110643712007</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>58.652190720000007</v>
       </c>
       <c r="Z10">
@@ -4249,31 +4272,31 @@
       </c>
       <c r="AE10">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="5"/>
-        <v>24.885286634057149</v>
+        <f t="shared" si="6"/>
+        <v>24.862663646208006</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="6"/>
-        <v>3.452603101154744</v>
+        <f t="shared" si="7"/>
+        <v>3.4494643710627853</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="7"/>
-        <v>6.905206202309488</v>
+        <f t="shared" si="8"/>
+        <v>6.8989287421255705</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="10"/>
-        <v>3.5243095937521382E-2</v>
+        <f t="shared" si="11"/>
+        <v>3.5211056759396363E-2</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
@@ -4334,15 +4357,15 @@
         <v>6.25</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7241.0112000000008</v>
       </c>
       <c r="R11">
@@ -4362,19 +4385,19 @@
         <v>7241.0112000000008</v>
       </c>
       <c r="V11">
-        <f>$T11*F11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="W11">
-        <f>$T11*G11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="X11">
-        <f>$T11*H11</f>
+        <f t="shared" si="0"/>
         <v>542.49655910400008</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>144.82022400000002</v>
       </c>
       <c r="Z11">
@@ -4399,31 +4422,31 @@
       </c>
       <c r="AE11">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="5"/>
-        <v>61.44515218285715</v>
+        <f t="shared" si="6"/>
+        <v>61.389292953600012</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="6"/>
-        <v>8.5249459287771447</v>
+        <f t="shared" si="7"/>
+        <v>8.5171959779328024</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="7"/>
-        <v>17.049891857554289</v>
+        <f t="shared" si="8"/>
+        <v>17.034391955865605</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="10"/>
-        <v>8.7019989969188583E-2</v>
+        <f t="shared" si="11"/>
+        <v>8.6940880887398417E-2</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
@@ -4484,15 +4507,15 @@
         <v>6.25</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.15743999999999997</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14641919999999997</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5886.0518399999992</v>
       </c>
       <c r="R12">
@@ -4512,19 +4535,19 @@
         <v>5886.0518399999992</v>
       </c>
       <c r="V12">
-        <f>$T12*F12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="W12">
-        <f>$T12*G12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="X12">
-        <f>$T12*H12</f>
+        <f t="shared" si="0"/>
         <v>440.98300385279992</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>117.72103679999998</v>
       </c>
       <c r="Z12">
@@ -4549,31 +4572,31 @@
       </c>
       <c r="AE12">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="5"/>
-        <v>49.947354185142849</v>
+        <f t="shared" si="6"/>
+        <v>49.901947499519999</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="6"/>
-        <v>6.929732917686855</v>
+        <f t="shared" si="7"/>
+        <v>6.9234331604889583</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="7"/>
-        <v>13.85946583537371</v>
+        <f t="shared" si="8"/>
+        <v>13.846866320977917</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="10"/>
-        <v>7.0736552938203412E-2</v>
+        <f t="shared" si="11"/>
+        <v>7.0672246980986869E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4836,15 +4859,15 @@
         <v>2929.8913280000006</v>
       </c>
       <c r="V8">
-        <f>$T8*F8</f>
+        <f t="shared" ref="V8:X12" si="0">$T8*F8</f>
         <v>439.01491658752013</v>
       </c>
       <c r="W8">
-        <f>$T8*G8</f>
+        <f t="shared" si="0"/>
         <v>439.01491658752013</v>
       </c>
       <c r="X8">
-        <f>$T8*H8</f>
+        <f t="shared" si="0"/>
         <v>219.50745829376007</v>
       </c>
       <c r="Y8">
@@ -4873,31 +4896,31 @@
       </c>
       <c r="AE8">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF8">
         <f>U8*Z8*$AE8</f>
-        <v>24.862220697600009</v>
+        <v>24.83961867878401</v>
       </c>
       <c r="AG8">
-        <f t="shared" ref="AG8:AJ12" si="0">V8*AA8*$AE8</f>
-        <v>3.4494029160448014</v>
+        <f t="shared" ref="AG8:AJ12" si="1">V8*AA8*$AE8</f>
+        <v>3.4462670952120336</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="0"/>
-        <v>6.8988058320896029</v>
+        <f t="shared" si="1"/>
+        <v>6.8925341904240671</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK8">
         <f>SUM(AF8:AJ8)/1000</f>
-        <v>3.5210429445734409E-2</v>
+        <v>3.5178419964420109E-2</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.2">
@@ -4958,15 +4981,15 @@
         <v>6.25</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O12" si="1">J9*M9/N9</f>
+        <f t="shared" ref="O9:O12" si="2">J9*M9/N9</f>
         <v>0.23296000000000003</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:P12" si="2">O9*(1-K9)</f>
+        <f t="shared" ref="P9:P12" si="3">O9*(1-K9)</f>
         <v>0.18543616000000004</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q9:Q12" si="3">D9*E9*P9</f>
+        <f t="shared" ref="Q9:Q12" si="4">D9*E9*P9</f>
         <v>2966.9785600000009</v>
       </c>
       <c r="R9">
@@ -4986,19 +5009,19 @@
         <v>2966.9785600000009</v>
       </c>
       <c r="V9">
-        <f>$T9*F9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="W9">
-        <f>$T9*G9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="X9">
-        <f>$T9*H9</f>
+        <f t="shared" si="0"/>
         <v>222.28603371520003</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="4">Q9*R9</f>
+        <f t="shared" ref="Y9:Y12" si="5">Q9*R9</f>
         <v>59.339571200000023</v>
       </c>
       <c r="Z9">
@@ -5023,31 +5046,31 @@
       </c>
       <c r="AE9">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF9">
-        <f t="shared" ref="AF9:AF12" si="5">U9*Z9*$AE9</f>
-        <v>25.176932352000009</v>
+        <f t="shared" ref="AF9:AF12" si="6">U9*Z9*$AE9</f>
+        <v>25.154044231680007</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="0"/>
-        <v>3.4930662440960005</v>
+        <f t="shared" si="1"/>
+        <v>3.4898907293286405</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="0"/>
-        <v>6.9861324881920011</v>
+        <f t="shared" si="1"/>
+        <v>6.9797814586572811</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK9">
-        <f t="shared" ref="AK9:AK12" si="6">SUM(AF9:AJ9)/1000</f>
-        <v>3.5656131084288008E-2</v>
+        <f t="shared" ref="AK9:AK12" si="7">SUM(AF9:AJ9)/1000</f>
+        <v>3.5623716419665927E-2</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.2">
@@ -5108,15 +5131,15 @@
         <v>6.25</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2932.6095360000004</v>
       </c>
       <c r="R10">
@@ -5136,19 +5159,19 @@
         <v>2932.6095360000004</v>
       </c>
       <c r="V10">
-        <f>$T10*F10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="W10">
-        <f>$T10*G10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="X10">
-        <f>$T10*H10</f>
+        <f t="shared" si="0"/>
         <v>219.71110643712007</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>58.652190720000007</v>
       </c>
       <c r="Z10">
@@ -5173,31 +5196,31 @@
       </c>
       <c r="AE10">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="5"/>
-        <v>24.885286634057149</v>
+        <f t="shared" si="6"/>
+        <v>24.862663646208006</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="0"/>
-        <v>3.452603101154744</v>
+        <f t="shared" si="1"/>
+        <v>3.4494643710627853</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="0"/>
-        <v>6.905206202309488</v>
+        <f t="shared" si="1"/>
+        <v>6.8989287421255705</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="6"/>
-        <v>3.5243095937521382E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.5211056759396363E-2</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
@@ -5258,15 +5281,15 @@
         <v>6.25</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7241.0112000000008</v>
       </c>
       <c r="R11">
@@ -5286,19 +5309,19 @@
         <v>7241.0112000000008</v>
       </c>
       <c r="V11">
-        <f>$T11*F11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="W11">
-        <f>$T11*G11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="X11">
-        <f>$T11*H11</f>
+        <f t="shared" si="0"/>
         <v>542.49655910400008</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>144.82022400000002</v>
       </c>
       <c r="Z11">
@@ -5323,31 +5346,31 @@
       </c>
       <c r="AE11">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="5"/>
-        <v>61.44515218285715</v>
+        <f t="shared" si="6"/>
+        <v>61.389292953600012</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="0"/>
-        <v>8.5249459287771447</v>
+        <f t="shared" si="1"/>
+        <v>8.5171959779328024</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="0"/>
-        <v>17.049891857554289</v>
+        <f t="shared" si="1"/>
+        <v>17.034391955865605</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="6"/>
-        <v>8.7019989969188583E-2</v>
+        <f t="shared" si="7"/>
+        <v>8.6940880887398417E-2</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
@@ -5408,15 +5431,15 @@
         <v>6.25</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.15743999999999997</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14641919999999997</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5886.0518399999992</v>
       </c>
       <c r="R12">
@@ -5436,19 +5459,19 @@
         <v>5886.0518399999992</v>
       </c>
       <c r="V12">
-        <f>$T12*F12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="W12">
-        <f>$T12*G12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="X12">
-        <f>$T12*H12</f>
+        <f t="shared" si="0"/>
         <v>440.98300385279992</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>117.72103679999998</v>
       </c>
       <c r="Z12">
@@ -5473,31 +5496,31 @@
       </c>
       <c r="AE12">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="5"/>
-        <v>49.947354185142849</v>
+        <f t="shared" si="6"/>
+        <v>49.901947499519999</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="0"/>
-        <v>6.929732917686855</v>
+        <f t="shared" si="1"/>
+        <v>6.9234331604889583</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="0"/>
-        <v>13.85946583537371</v>
+        <f t="shared" si="1"/>
+        <v>13.846866320977917</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="6"/>
-        <v>7.0736552938203412E-2</v>
+        <f t="shared" si="7"/>
+        <v>7.0672246980986869E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5766,15 +5789,15 @@
         <v>2929.8913280000006</v>
       </c>
       <c r="V8">
-        <f>$T8*F8</f>
+        <f t="shared" ref="V8:X12" si="0">$T8*F8</f>
         <v>439.01491658752013</v>
       </c>
       <c r="W8">
-        <f>$T8*G8</f>
+        <f t="shared" si="0"/>
         <v>439.01491658752013</v>
       </c>
       <c r="X8">
-        <f>$T8*H8</f>
+        <f t="shared" si="0"/>
         <v>219.50745829376007</v>
       </c>
       <c r="Y8">
@@ -5806,19 +5829,19 @@
         <v>1757.9347968000004</v>
       </c>
       <c r="AF8">
-        <f t="shared" ref="AF8:AI8" si="0">V8*AA8</f>
+        <f t="shared" ref="AF8:AI8" si="1">V8*AA8</f>
         <v>109.75372914688003</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175.60596663500806</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.509239296000004</v>
       </c>
       <c r="AJ8">
@@ -5831,11 +5854,11 @@
       </c>
       <c r="AL8">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM8">
         <f>AJ8*AK8*AL8/1000</f>
-        <v>5.8376162701688841E-3</v>
+        <v>5.8323093462869123E-3</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
@@ -5896,15 +5919,15 @@
         <v>6.25</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O12" si="1">J9*M9/N9</f>
+        <f t="shared" ref="O9:O12" si="2">J9*M9/N9</f>
         <v>0.23296000000000003</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:P12" si="2">O9*(1-K9)</f>
+        <f t="shared" ref="P9:P12" si="3">O9*(1-K9)</f>
         <v>0.18543616000000004</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q9:Q12" si="3">D9*E9*P9</f>
+        <f t="shared" ref="Q9:Q12" si="4">D9*E9*P9</f>
         <v>2966.9785600000009</v>
       </c>
       <c r="R9">
@@ -5924,19 +5947,19 @@
         <v>2966.9785600000009</v>
       </c>
       <c r="V9">
-        <f>$T9*F9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="W9">
-        <f>$T9*G9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="X9">
-        <f>$T9*H9</f>
+        <f t="shared" si="0"/>
         <v>222.28603371520003</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="4">Q9*R9</f>
+        <f t="shared" ref="Y9:Y12" si="5">Q9*R9</f>
         <v>59.339571200000023</v>
       </c>
       <c r="Z9">
@@ -5960,27 +5983,27 @@
         <v>0.35</v>
       </c>
       <c r="AE9">
-        <f t="shared" ref="AE9:AE12" si="5">U9*Z9</f>
+        <f t="shared" ref="AE9:AE12" si="6">U9*Z9</f>
         <v>1780.1871360000005</v>
       </c>
       <c r="AF9">
-        <f t="shared" ref="AF9:AF12" si="6">V9*AA9</f>
+        <f t="shared" ref="AF9:AF12" si="7">V9*AA9</f>
         <v>111.14301685760002</v>
       </c>
       <c r="AG9">
-        <f t="shared" ref="AG9:AG12" si="7">W9*AB9</f>
+        <f t="shared" ref="AG9:AG12" si="8">W9*AB9</f>
         <v>177.82882697216004</v>
       </c>
       <c r="AH9">
-        <f t="shared" ref="AH9:AH12" si="8">X9*AC9</f>
+        <f t="shared" ref="AH9:AH12" si="9">X9*AC9</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f t="shared" ref="AI9:AI12" si="9">Y9*AD9</f>
+        <f t="shared" ref="AI9:AI12" si="10">Y9*AD9</f>
         <v>20.768849920000008</v>
       </c>
       <c r="AJ9">
-        <f t="shared" ref="AJ9:AJ12" si="10">SUM(AE9:AI9)</f>
+        <f t="shared" ref="AJ9:AJ12" si="11">SUM(AE9:AI9)</f>
         <v>2089.9278297497603</v>
       </c>
       <c r="AK9">
@@ -5989,11 +6012,11 @@
       </c>
       <c r="AL9">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM9">
-        <f t="shared" ref="AM9:AM12" si="11">AJ9*AK9*AL9/1000</f>
-        <v>1.9376616592965631E-2</v>
+        <f t="shared" ref="AM9:AM12" si="12">AJ9*AK9*AL9/1000</f>
+        <v>1.9359001486972029E-2</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
@@ -6054,15 +6077,15 @@
         <v>6.25</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2932.6095360000004</v>
       </c>
       <c r="R10">
@@ -6082,19 +6105,19 @@
         <v>2932.6095360000004</v>
       </c>
       <c r="V10">
-        <f>$T10*F10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="W10">
-        <f>$T10*G10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="X10">
-        <f>$T10*H10</f>
+        <f t="shared" si="0"/>
         <v>219.71110643712007</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>58.652190720000007</v>
       </c>
       <c r="Z10">
@@ -6118,27 +6141,27 @@
         <v>0.35</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1759.5657216000002</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>109.85555321856003</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>175.76888514969608</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20.528266752</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2065.7184267202565</v>
       </c>
       <c r="AK10">
@@ -6147,11 +6170,11 @@
       </c>
       <c r="AL10">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM10">
-        <f t="shared" si="11"/>
-        <v>2.2722902693922818E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.2702245509655619E-2</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
@@ -6212,15 +6235,15 @@
         <v>6.25</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7241.0112000000008</v>
       </c>
       <c r="R11">
@@ -6240,19 +6263,19 @@
         <v>7241.0112000000008</v>
       </c>
       <c r="V11">
-        <f>$T11*F11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="W11">
-        <f>$T11*G11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="X11">
-        <f>$T11*H11</f>
+        <f t="shared" si="0"/>
         <v>542.49655910400008</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>144.82022400000002</v>
       </c>
       <c r="Z11">
@@ -6276,27 +6299,27 @@
         <v>0.35</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4344.6067200000007</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>271.24827955200004</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>433.99724728320007</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>50.687078400000004</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5100.5393252352005</v>
       </c>
       <c r="AK11">
@@ -6305,11 +6328,11 @@
       </c>
       <c r="AL11">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM11">
-        <f t="shared" si="11"/>
-        <v>2.324388635357184E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.3222755547795865E-2</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
@@ -6370,15 +6393,15 @@
         <v>6.25</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.15743999999999997</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14641919999999997</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5886.0518399999992</v>
       </c>
       <c r="R12">
@@ -6398,19 +6421,19 @@
         <v>5886.0518399999992</v>
       </c>
       <c r="V12">
-        <f>$T12*F12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="W12">
-        <f>$T12*G12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="X12">
-        <f>$T12*H12</f>
+        <f t="shared" si="0"/>
         <v>440.98300385279992</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>117.72103679999998</v>
       </c>
       <c r="Z12">
@@ -6434,27 +6457,27 @@
         <v>0.35</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3531.6311039999996</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>220.49150192639996</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>352.78640308223999</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>41.202362879999988</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4146.111371888639</v>
       </c>
       <c r="AK12">
@@ -6463,11 +6486,11 @@
       </c>
       <c r="AL12">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM12">
-        <f t="shared" si="11"/>
-        <v>5.2122542960885754E-2</v>
+        <f t="shared" si="12"/>
+        <v>5.2075158830921307E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6736,15 +6759,15 @@
         <v>2929.8913280000006</v>
       </c>
       <c r="V8">
-        <f>$T8*F8</f>
+        <f t="shared" ref="V8:X12" si="0">$T8*F8</f>
         <v>439.01491658752013</v>
       </c>
       <c r="W8">
-        <f>$T8*G8</f>
+        <f t="shared" si="0"/>
         <v>439.01491658752013</v>
       </c>
       <c r="X8">
-        <f>$T8*H8</f>
+        <f t="shared" si="0"/>
         <v>219.50745829376007</v>
       </c>
       <c r="Y8">
@@ -6776,19 +6799,19 @@
         <v>1757.9347968000004</v>
       </c>
       <c r="AF8">
-        <f t="shared" ref="AF8:AI12" si="0">V8*AA8</f>
+        <f t="shared" ref="AF8:AI12" si="1">V8*AA8</f>
         <v>109.75372914688003</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175.60596663500806</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.509239296000004</v>
       </c>
       <c r="AJ8">
@@ -6801,11 +6824,11 @@
       </c>
       <c r="AL8">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM8">
         <f>AJ8*AK8*AL8/1000</f>
-        <v>5.8376162701688841E-3</v>
+        <v>5.8323093462869123E-3</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
@@ -6866,15 +6889,15 @@
         <v>6.25</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O12" si="1">J9*M9/N9</f>
+        <f t="shared" ref="O9:O12" si="2">J9*M9/N9</f>
         <v>0.23296000000000003</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:P12" si="2">O9*(1-K9)</f>
+        <f t="shared" ref="P9:P12" si="3">O9*(1-K9)</f>
         <v>0.18543616000000004</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q9:Q12" si="3">D9*E9*P9</f>
+        <f t="shared" ref="Q9:Q12" si="4">D9*E9*P9</f>
         <v>2966.9785600000009</v>
       </c>
       <c r="R9">
@@ -6894,19 +6917,19 @@
         <v>2966.9785600000009</v>
       </c>
       <c r="V9">
-        <f>$T9*F9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="W9">
-        <f>$T9*G9</f>
+        <f t="shared" si="0"/>
         <v>444.57206743040007</v>
       </c>
       <c r="X9">
-        <f>$T9*H9</f>
+        <f t="shared" si="0"/>
         <v>222.28603371520003</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="4">Q9*R9</f>
+        <f t="shared" ref="Y9:Y12" si="5">Q9*R9</f>
         <v>59.339571200000023</v>
       </c>
       <c r="Z9">
@@ -6930,27 +6953,27 @@
         <v>0.35</v>
       </c>
       <c r="AE9">
-        <f t="shared" ref="AE9:AE12" si="5">U9*Z9</f>
+        <f t="shared" ref="AE9:AE12" si="6">U9*Z9</f>
         <v>1780.1871360000005</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>111.14301685760002</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>177.82882697216004</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.768849920000008</v>
       </c>
       <c r="AJ9">
-        <f t="shared" ref="AJ9:AJ12" si="6">SUM(AE9:AI9)</f>
+        <f t="shared" ref="AJ9:AJ12" si="7">SUM(AE9:AI9)</f>
         <v>2089.9278297497603</v>
       </c>
       <c r="AK9">
@@ -6959,11 +6982,11 @@
       </c>
       <c r="AL9">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM9">
-        <f t="shared" ref="AM9:AM12" si="7">AJ9*AK9*AL9/1000</f>
-        <v>1.9376616592965631E-2</v>
+        <f t="shared" ref="AM9:AM12" si="8">AJ9*AK9*AL9/1000</f>
+        <v>1.9359001486972029E-2</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
@@ -7024,15 +7047,15 @@
         <v>6.25</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2932.6095360000004</v>
       </c>
       <c r="R10">
@@ -7052,19 +7075,19 @@
         <v>2932.6095360000004</v>
       </c>
       <c r="V10">
-        <f>$T10*F10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="W10">
-        <f>$T10*G10</f>
+        <f t="shared" si="0"/>
         <v>439.42221287424013</v>
       </c>
       <c r="X10">
-        <f>$T10*H10</f>
+        <f t="shared" si="0"/>
         <v>219.71110643712007</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>58.652190720000007</v>
       </c>
       <c r="Z10">
@@ -7088,27 +7111,27 @@
         <v>0.35</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1759.5657216000002</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>109.85555321856003</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175.76888514969608</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.528266752</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2065.7184267202565</v>
       </c>
       <c r="AK10">
@@ -7117,11 +7140,11 @@
       </c>
       <c r="AL10">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM10">
-        <f t="shared" si="7"/>
-        <v>2.2722902693922818E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.2702245509655619E-2</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
@@ -7182,15 +7205,15 @@
         <v>6.25</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7241.0112000000008</v>
       </c>
       <c r="R11">
@@ -7210,19 +7233,19 @@
         <v>7241.0112000000008</v>
       </c>
       <c r="V11">
-        <f>$T11*F11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="W11">
-        <f>$T11*G11</f>
+        <f t="shared" si="0"/>
         <v>1084.9931182080002</v>
       </c>
       <c r="X11">
-        <f>$T11*H11</f>
+        <f t="shared" si="0"/>
         <v>542.49655910400008</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>144.82022400000002</v>
       </c>
       <c r="Z11">
@@ -7246,27 +7269,27 @@
         <v>0.35</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4344.6067200000007</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>271.24827955200004</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>433.99724728320007</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50.687078400000004</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5100.5393252352005</v>
       </c>
       <c r="AK11">
@@ -7275,11 +7298,11 @@
       </c>
       <c r="AL11">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM11">
-        <f t="shared" si="7"/>
-        <v>2.324388635357184E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.3222755547795865E-2</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
@@ -7340,15 +7363,15 @@
         <v>6.25</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.15743999999999997</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14641919999999997</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5886.0518399999992</v>
       </c>
       <c r="R12">
@@ -7368,19 +7391,19 @@
         <v>5886.0518399999992</v>
       </c>
       <c r="V12">
-        <f>$T12*F12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="W12">
-        <f>$T12*G12</f>
+        <f t="shared" si="0"/>
         <v>881.96600770559985</v>
       </c>
       <c r="X12">
-        <f>$T12*H12</f>
+        <f t="shared" si="0"/>
         <v>440.98300385279992</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>117.72103679999998</v>
       </c>
       <c r="Z12">
@@ -7404,27 +7427,27 @@
         <v>0.35</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3531.6311039999996</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>220.49150192639996</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>352.78640308223999</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41.202362879999988</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4146.111371888639</v>
       </c>
       <c r="AK12">
@@ -7433,11 +7456,11 @@
       </c>
       <c r="AL12">
         <f>Constants!$B$33</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AM12">
-        <f t="shared" si="7"/>
-        <v>5.2122542960885754E-2</v>
+        <f t="shared" si="8"/>
+        <v>5.2075158830921307E-2</v>
       </c>
     </row>
   </sheetData>
